--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N73_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N73_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>56.28436155168864</v>
+        <v>9.146208752149404</v>
       </c>
       <c r="D2" t="n">
-        <v>55.26143030190537</v>
+        <v>8.979982424059623</v>
       </c>
       <c r="E2" t="n">
-        <v>14.67283993536097</v>
+        <v>2.384336489496157</v>
       </c>
       <c r="F2" t="n">
-        <v>15.20906602310732</v>
+        <v>2.471473228754939</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.21330530284659</v>
+        <v>6.209662111712571</v>
       </c>
       <c r="D3" t="n">
-        <v>35.71231447750716</v>
+        <v>5.803251102594913</v>
       </c>
       <c r="E3" t="n">
-        <v>14.67283993536097</v>
+        <v>2.384336489496157</v>
       </c>
       <c r="F3" t="n">
-        <v>15.20906602310732</v>
+        <v>2.471473228754939</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>65.20027645403486</v>
+        <v>10.59504492378067</v>
       </c>
       <c r="D4" t="n">
-        <v>65.50473281026015</v>
+        <v>10.64451908166727</v>
       </c>
       <c r="E4" t="n">
-        <v>14.67283993536097</v>
+        <v>2.384336489496157</v>
       </c>
       <c r="F4" t="n">
-        <v>15.20906602310732</v>
+        <v>2.471473228754939</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.04614189052456</v>
+        <v>3.09499805721024</v>
       </c>
       <c r="D5" t="n">
-        <v>18.29334268996274</v>
+        <v>2.972668187118946</v>
       </c>
       <c r="E5" t="n">
-        <v>14.67283993536097</v>
+        <v>2.384336489496157</v>
       </c>
       <c r="F5" t="n">
-        <v>15.20906602310732</v>
+        <v>2.471473228754939</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.24959419101463</v>
+        <v>5.728059056039878</v>
       </c>
       <c r="D6" t="n">
-        <v>34.49035452815026</v>
+        <v>5.604682610824417</v>
       </c>
       <c r="E6" t="n">
-        <v>14.67283993536097</v>
+        <v>2.384336489496157</v>
       </c>
       <c r="F6" t="n">
-        <v>15.20906602310732</v>
+        <v>2.471473228754939</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>50.83979458435505</v>
+        <v>8.261466619957696</v>
       </c>
       <c r="D7" t="n">
-        <v>51.50310810244433</v>
+        <v>8.369255066647204</v>
       </c>
       <c r="E7" t="n">
-        <v>14.67283993536097</v>
+        <v>2.384336489496157</v>
       </c>
       <c r="F7" t="n">
-        <v>15.20906602310732</v>
+        <v>2.471473228754939</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>38.55922009245184</v>
+        <v>6.265873265023424</v>
       </c>
       <c r="D8" t="n">
-        <v>37.94707274765556</v>
+        <v>6.166399321494029</v>
       </c>
       <c r="E8" t="n">
-        <v>14.67283993536097</v>
+        <v>2.384336489496157</v>
       </c>
       <c r="F8" t="n">
-        <v>15.20906602310732</v>
+        <v>2.471473228754939</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>65.20555078771284</v>
+        <v>10.59590200300334</v>
       </c>
       <c r="D9" t="n">
-        <v>65.91939438276</v>
+        <v>10.7119015871985</v>
       </c>
       <c r="E9" t="n">
-        <v>14.67283993536097</v>
+        <v>2.384336489496157</v>
       </c>
       <c r="F9" t="n">
-        <v>15.20906602310732</v>
+        <v>2.471473228754939</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>46.74209378687011</v>
+        <v>7.595590240366393</v>
       </c>
       <c r="D10" t="n">
-        <v>46.43776078095586</v>
+        <v>7.546136126905327</v>
       </c>
       <c r="E10" t="n">
-        <v>14.67283993536097</v>
+        <v>2.384336489496157</v>
       </c>
       <c r="F10" t="n">
-        <v>15.20906602310732</v>
+        <v>2.471473228754939</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>40.61179703763748</v>
+        <v>6.599417018616091</v>
       </c>
       <c r="D11" t="n">
-        <v>40.56264940639903</v>
+        <v>6.591430528539843</v>
       </c>
       <c r="E11" t="n">
-        <v>14.67283993536097</v>
+        <v>2.384336489496157</v>
       </c>
       <c r="F11" t="n">
-        <v>15.20906602310732</v>
+        <v>2.471473228754939</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>69.40790104366428</v>
+        <v>11.27878391959545</v>
       </c>
       <c r="D12" t="n">
-        <v>69.92990299719841</v>
+        <v>11.36360923704474</v>
       </c>
       <c r="E12" t="n">
-        <v>14.67283993536097</v>
+        <v>2.384336489496157</v>
       </c>
       <c r="F12" t="n">
-        <v>15.20906602310732</v>
+        <v>2.471473228754939</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
